--- a/CredAlumnos/IEUM MAPPING 2024 10 04 OK - copia.xlsx
+++ b/CredAlumnos/IEUM MAPPING 2024 10 04 OK - copia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Flowers\Santander\Adicionales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abraham\Desktop\Cosas cosas\Proy_Credenciales\CredAlumnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E538A051-C404-45E8-A586-648173296842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC99A52-9F25-4031-BC42-6F57F1AF9EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CE22293A-17E7-4ACF-A499-9237F8422D25}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CE22293A-17E7-4ACF-A499-9237F8422D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Condición" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:FV"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -39,9 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="258">
   <si>
-    <t>INGENIERIA MECATRONICA</t>
-  </si>
-  <si>
     <t>INGENIERIA INDUSTRIAL Y DE SISTEMAS</t>
   </si>
   <si>
@@ -811,6 +811,9 @@
   </si>
   <si>
     <t>MAESTRIA EN DIRECCION DE NEGOCIOS Y DESARROLLO EMPRESARIAL</t>
+  </si>
+  <si>
+    <t>INGENIERIA EN MECATRONICA</t>
   </si>
 </sst>
 </file>
@@ -1195,132 +1198,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88BC92D8-5180-44EE-A3F4-2D0D909F4C56}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1331,1339 +1334,1339 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76FD6B72-BE62-49D6-A03B-CDFD40FA0E32}">
   <dimension ref="A1:D120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" style="2"/>
-    <col min="3" max="3" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="2"/>
+    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C37" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C58" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D58" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D59" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C60" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D60" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C61" t="s">
+        <v>246</v>
+      </c>
+      <c r="D61" t="s">
         <v>247</v>
       </c>
-      <c r="D61" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>101</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>102</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>103</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C64" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>104</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>105</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>106</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>107</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>108</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>109</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>110</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C71" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>111</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>112</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>113</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C74" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>114</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>115</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C76" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>116</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>117</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>118</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C79" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>119</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C80" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>120</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C81" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>121</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C82" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>122</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>123</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>124</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C85" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>125</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>126</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C87" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>127</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C88" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>128</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C89" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>129</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C90" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>130</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C91" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>131</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>132</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>133</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C94" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>134</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C95" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>135</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>136</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C97" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>137</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>138</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>139</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C100" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>165</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>166</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>202</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C103" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>203</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C104" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>204</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>205</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C106" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>206</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C107" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>301</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C108" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>302</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C109" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>303</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C110" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>304</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C111" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>305</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C112" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>401</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C113" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>402</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C114" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>403</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C115" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>404</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>405</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>406</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C118" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>500</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>501</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C120" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2679,49 +2682,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B676B8D3-9E7E-4A73-9153-4D09A694AECF}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="2"/>
+    <col min="1" max="1" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2730,6 +2733,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C58A9BC3874DAA408B49BD4F553E46CA" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="54ac547d7294c45256152878f4ec1baf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d21d6be6-bcc6-4990-af08-ccc00de007cf" xmlns:ns3="bdb4bb3f-5a9e-44e5-baa1-27db6e503f66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f50bf97d6954956598014d786f2d7d9" ns2:_="" ns3:_="">
     <xsd:import namespace="d21d6be6-bcc6-4990-af08-ccc00de007cf"/>
@@ -2958,22 +2976,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77294A9A-3453-43D0-8684-3A574EFD2D77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECEA16C9-65DE-48E3-AABD-409349DF4399}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B437FD2-739A-48DD-978B-E21A37FBFF39}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2990,21 +3010,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECEA16C9-65DE-48E3-AABD-409349DF4399}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77294A9A-3453-43D0-8684-3A574EFD2D77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>